--- a/data/trans_orig/IP25A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48755</t>
+          <t>48558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>53177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51857</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103649</t>
+          <t>104183</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108964</t>
+          <t>108966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74184</t>
+          <t>74127</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56335</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77472</t>
+          <t>77853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113767</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146958</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172303</t>
+          <t>172360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194976</t>
+          <t>194773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164997</t>
+          <t>164616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>186134</t>
+          <t>186108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>341998</t>
+          <t>343344</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375189</t>
+          <t>375975</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,89%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43959</t>
+          <t>43224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>61511</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>57689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76137</t>
+          <t>76767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105055</t>
+          <t>107161</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131273</t>
+          <t>131307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63392</t>
+          <t>63951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81503</t>
+          <t>82238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58552</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77061</t>
+          <t>77000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128878</t>
+          <t>128844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155096</t>
+          <t>152990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,81%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>94535</t>
+          <t>95466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115908</t>
+          <t>118110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96206</t>
+          <t>96556</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118801</t>
+          <t>118397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197031</t>
+          <t>197226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>229345</t>
+          <t>230036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72149</t>
+          <t>69947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93522</t>
+          <t>92591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80168</t>
+          <t>80572</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102763</t>
+          <t>102413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>157681</t>
+          <t>156990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189995</t>
+          <t>189800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>204283</t>
+          <t>203162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241902</t>
+          <t>242286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221272</t>
+          <t>220854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>262514</t>
+          <t>261072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436116</t>
+          <t>438107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>490173</t>
+          <t>491761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371848</t>
+          <t>371464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>410588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>369435</t>
+          <t>370877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410677</t>
+          <t>411095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>755526</t>
+          <t>753938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>809583</t>
+          <t>807592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>20661</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72758</t>
+          <t>72781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80719</t>
+          <t>80318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73246</t>
+          <t>73030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82731</t>
+          <t>82573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149371</t>
+          <t>149836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161756</t>
+          <t>161418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64796</t>
+          <t>62649</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87818</t>
+          <t>86807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83062</t>
+          <t>83178</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110539</t>
+          <t>110589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150995</t>
+          <t>153696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187983</t>
+          <t>189616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140733</t>
+          <t>141744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163755</t>
+          <t>165902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>154946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182473</t>
+          <t>182357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>306103</t>
+          <t>304470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>343091</t>
+          <t>340390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>57229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77439</t>
+          <t>77107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>81091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>123517</t>
+          <t>122491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152480</t>
+          <t>151794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76812</t>
+          <t>77144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97533</t>
+          <t>97022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73800</t>
+          <t>74510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>94007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157372</t>
+          <t>158058</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186335</t>
+          <t>187361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67953</t>
+          <t>65893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89248</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62395</t>
+          <t>63299</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84247</t>
+          <t>84234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134859</t>
+          <t>136336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165215</t>
+          <t>165614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77030</t>
+          <t>78150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98325</t>
+          <t>100385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90085</t>
+          <t>90098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111937</t>
+          <t>111033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>175395</t>
+          <t>174996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205751</t>
+          <t>204274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,97%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205233</t>
+          <t>204560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>228621</t>
+          <t>228526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>267905</t>
+          <t>269667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>445925</t>
+          <t>443391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>503374</t>
+          <t>498740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385389</t>
+          <t>387354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426770</t>
+          <t>427443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415137</t>
+          <t>413375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454421</t>
+          <t>454516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>811671</t>
+          <t>816305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869120</t>
+          <t>871654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>34867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>54677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64548</t>
+          <t>64620</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55946</t>
+          <t>55328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114707</t>
+          <t>113896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128755</t>
+          <t>128997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77119</t>
+          <t>77650</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100360</t>
+          <t>99558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>94090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122393</t>
+          <t>120182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>179652</t>
+          <t>178414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212466</t>
+          <t>212228</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99591</t>
+          <t>100393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122832</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>125667</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>151685</t>
+          <t>153970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235545</t>
+          <t>235783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268359</t>
+          <t>269597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69570</t>
+          <t>69025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91728</t>
+          <t>90952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82164</t>
+          <t>82153</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158622</t>
+          <t>156597</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190905</t>
+          <t>189089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91493</t>
+          <t>92269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>113651</t>
+          <t>114196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81222</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>104044</t>
+          <t>104055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178524</t>
+          <t>180340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210807</t>
+          <t>212832</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87947</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108819</t>
+          <t>108547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79461</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100763</t>
+          <t>99985</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173499</t>
+          <t>173987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203051</t>
+          <t>203872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78842</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63674</t>
+          <t>64452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84976</t>
+          <t>86155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128175</t>
+          <t>127354</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157727</t>
+          <t>157239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>259939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300004</t>
+          <t>298730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285822</t>
+          <t>284906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>329572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>556494</t>
+          <t>559183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>617007</t>
+          <t>616350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322368</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>362433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346857</t>
+          <t>345484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389234</t>
+          <t>390150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>680421</t>
+          <t>681078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>740934</t>
+          <t>738245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3656</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1878</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5186</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5267</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55175</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52167</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55823</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>51866</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48558</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53177</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48477</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>53182</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55175</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52152</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55823</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104183</t>
+          <t>103811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108966</t>
+          <t>108945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55823</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55823</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>53744</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>53744</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>53744</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>55823</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>55823</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>55823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>66536</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>55393</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>77111</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>62990</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51714</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74127</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>52222</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>74770</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>66536</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>56361</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>77853</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112981</t>
+          <t>113561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145612</t>
+          <t>146050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>175933</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>165358</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>187076</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>183497</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>172360</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>194773</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>171717</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>194265</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>175933</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>164616</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>186108</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,56%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343344</t>
+          <t>342906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375975</t>
+          <t>375395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>242469</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>242469</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>242469</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>246487</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>246487</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>246487</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>242469</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>242469</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>242469</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66684</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57381</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76516</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>42,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>51795</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43224</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>61511</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>42920</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>60862</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66684</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>57689</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>76767</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107161</t>
+          <t>105403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131307</t>
+          <t>130937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>68005</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58173</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77308</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>73667</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63951</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>82238</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>64600</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>82542</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68005</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57922</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77000</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128844</t>
+          <t>129214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>152990</t>
+          <t>154748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>134689</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>134689</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>134689</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>125462</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>125462</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>125462</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>134689</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>134689</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>134689</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>107604</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>96966</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>118743</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>59,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>106403</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>95466</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>118110</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>93906</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>116787</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>56,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>107604</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>96556</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>118397</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,08%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>197226</t>
+          <t>197025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>230036</t>
+          <t>229366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91365</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80226</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>102003</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>81654</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69947</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92591</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>71270</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>94151</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>43,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>91365</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80572</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>102413</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156990</t>
+          <t>157660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189800</t>
+          <t>190001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>198969</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>198969</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>198969</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188057</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>188057</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>188057</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>198969</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>198969</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>198969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>222136</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>262108</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>203162</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>242286</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>203647</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>241490</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>220854</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>261072</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438107</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>491761</t>
+          <t>492547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>390478</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>369841</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>409813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>390685</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>371464</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>410588</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>372260</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>63,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>66,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>390478</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>370877</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>411095</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>753938</t>
+          <t>753152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807592</t>
+          <t>807690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>631949</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>631949</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>631949</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>613750</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>631949</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>631949</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>631949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2484,13 +2484,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14141</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5368</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10142</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2571</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10147</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14544</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>21236</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78876</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73433</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82983</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>77555</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72781</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80318</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72776</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80352</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,53%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78876</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>73030</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82573</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149836</t>
+          <t>149261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161418</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -2900,52 +2900,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>87574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>87574</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>87574</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>82923</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>82923</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>82923</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>87574</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>87574</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>87574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>95666</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82515</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>109266</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>31,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>74655</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62649</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>86807</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>63262</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>86921</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>32,66%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>95666</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>83178</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>110589</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,03%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153696</t>
+          <t>153224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189616</t>
+          <t>187931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>169869</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>156269</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>183020</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>153896</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>141744</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>165902</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>141630</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>165289</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>67,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>169869</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>154946</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>182357</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>63,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304470</t>
+          <t>306155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>340390</t>
+          <t>340862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>265535</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>265535</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>265535</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228551</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228551</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228551</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>265535</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>265535</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>265535</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70750</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60831</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82263</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>52,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>67101</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57229</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77107</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>55296</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76012</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>43,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70750</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61594</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>81091</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122491</t>
+          <t>124168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151794</t>
+          <t>152312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>84851</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>73338</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94770</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>54,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>87150</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77144</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>97022</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78239</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>98955</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>56,5%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>84851</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>74510</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>94007</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>54,53%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158058</t>
+          <t>157540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187361</t>
+          <t>185684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155601</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155601</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155601</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154251</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154251</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154251</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>155601</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>155601</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3703,67 +3703,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>73116</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>62550</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83672</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>77274</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>65893</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>88128</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>66654</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>87878</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>73116</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>63299</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84234</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136336</t>
+          <t>137142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165614</t>
+          <t>164639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>101216</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90660</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>111782</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>89004</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>78150</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100385</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>78400</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99624</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,37%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>101216</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>90098</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>111033</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>174996</t>
+          <t>175971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>204274</t>
+          <t>203468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,74%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174332</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174332</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166278</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166278</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166278</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174332</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174332</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>228270</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>270779</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>204560</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>244649</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>204349</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>246544</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>228526</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>269667</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>443391</t>
+          <t>445637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>498740</t>
+          <t>501424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>434813</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>454772</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>591</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>407605</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>387354</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>427443</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>385459</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>427654</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>434813</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>413375</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>454516</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816305</t>
+          <t>813621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871654</t>
+          <t>869408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>683042</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>683042</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>683042</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>632003</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>632003</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>632003</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>683042</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>683042</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>683042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,13 +4431,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14717</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9919</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20926</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>12042</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7791</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17734</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18255</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14717</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9818</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34867</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61635</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55426</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66433</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>60369</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54677</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>64620</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54156</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64341</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>83,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61635</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55328</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>66534</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113896</t>
+          <t>113480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128997</t>
+          <t>128664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76352</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76352</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76352</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>72411</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>72411</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>72411</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76352</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76352</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76352</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>108567</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>94249</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>120818</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>43,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>87870</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>77650</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>99558</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>76821</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>98754</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>43,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>49,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>108567</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>94090</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>120182</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178414</t>
+          <t>180710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>212228</t>
+          <t>212819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>139493</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>127242</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>153811</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>56,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>51,3%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>62,01%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>112081</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100393</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>122301</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>101197</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>123130</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>56,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>50,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>139493</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>127878</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>153970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>235783</t>
+          <t>235192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269597</t>
+          <t>267301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,66%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>248060</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>248060</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>248060</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>316</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>199951</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>199951</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>199951</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>248060</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>248060</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>248060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93436</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81479</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>104010</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>80805</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>69025</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>90952</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>69219</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90937</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>93436</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>82153</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>105283</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156597</t>
+          <t>158901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189089</t>
+          <t>190840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,66%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92772</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82198</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>104729</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>102416</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>92269</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>114196</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>92284</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114002</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>55,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92772</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80925</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104055</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180340</t>
+          <t>178589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212832</t>
+          <t>210528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>186208</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>186208</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>186208</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>183221</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>183221</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>183221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>186208</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>186208</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>186208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>90343</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>80378</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>100742</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,88%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>61,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>98318</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>87834</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>108547</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>87390</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>108930</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>58,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>52,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>90343</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>78282</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>99985</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173987</t>
+          <t>174919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>203872</t>
+          <t>203447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74094</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63695</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>84059</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>68471</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58242</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78955</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>57859</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>79399</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>41,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>47,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>74094</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>64452</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>86155</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127354</t>
+          <t>127779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157239</t>
+          <t>156307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164437</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164437</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164437</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>164437</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>164437</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>164437</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>285940</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>329699</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>279034</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>259939</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>298730</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>260763</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>300181</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>284906</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>329572</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>559183</t>
+          <t>558745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>616350</t>
+          <t>613965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>367993</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>345357</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>389116</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>343338</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>323642</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>362433</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322191</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>361609</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>55,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>367993</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>345484</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>390150</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>54,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681078</t>
+          <t>683463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738245</t>
+          <t>738683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>622372</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>622372</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>622372</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
